--- a/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0003T0006Z000C1N12_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0003T0006Z000C1N12_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>3.453865421271634</v>
+        <v>0.5612531309566406</v>
       </c>
       <c r="D2" t="n">
-        <v>3.314328442588778</v>
+        <v>0.5385783719206764</v>
       </c>
       <c r="E2" t="n">
-        <v>19.14907586987314</v>
+        <v>3.111724828854385</v>
       </c>
       <c r="F2" t="n">
-        <v>19.44898639194725</v>
+        <v>3.160460288691429</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>61.11683028080677</v>
+        <v>9.931484920631101</v>
       </c>
       <c r="D3" t="n">
-        <v>60.38232603654732</v>
+        <v>9.812127980938939</v>
       </c>
       <c r="E3" t="n">
-        <v>19.14907586987314</v>
+        <v>3.111724828854385</v>
       </c>
       <c r="F3" t="n">
-        <v>19.44898639194725</v>
+        <v>3.160460288691429</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>38.34055052048184</v>
+        <v>6.2303394595783</v>
       </c>
       <c r="D4" t="n">
-        <v>37.45250662712047</v>
+        <v>6.086032326907077</v>
       </c>
       <c r="E4" t="n">
-        <v>19.14907586987314</v>
+        <v>3.111724828854385</v>
       </c>
       <c r="F4" t="n">
-        <v>19.44898639194725</v>
+        <v>3.160460288691429</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>29.4901264705003</v>
+        <v>4.792145551456299</v>
       </c>
       <c r="D5" t="n">
-        <v>28.75934013564812</v>
+        <v>4.673392772042819</v>
       </c>
       <c r="E5" t="n">
-        <v>19.14907586987314</v>
+        <v>3.111724828854385</v>
       </c>
       <c r="F5" t="n">
-        <v>19.44898639194725</v>
+        <v>3.160460288691429</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>34.63890092374081</v>
+        <v>5.628821400107881</v>
       </c>
       <c r="D6" t="n">
-        <v>34.07122011928237</v>
+        <v>5.536573269383385</v>
       </c>
       <c r="E6" t="n">
-        <v>19.14907586987314</v>
+        <v>3.111724828854385</v>
       </c>
       <c r="F6" t="n">
-        <v>19.44898639194725</v>
+        <v>3.160460288691429</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>27.25066085197394</v>
+        <v>4.428232388445765</v>
       </c>
       <c r="D7" t="n">
-        <v>26.75737570588021</v>
+        <v>4.348073552205535</v>
       </c>
       <c r="E7" t="n">
-        <v>19.14907586987314</v>
+        <v>3.111724828854385</v>
       </c>
       <c r="F7" t="n">
-        <v>19.44898639194725</v>
+        <v>3.160460288691429</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>31.29974529853573</v>
+        <v>5.086208611012057</v>
       </c>
       <c r="D8" t="n">
-        <v>31.08919126690355</v>
+        <v>5.051993580871827</v>
       </c>
       <c r="E8" t="n">
-        <v>19.14907586987314</v>
+        <v>3.111724828854385</v>
       </c>
       <c r="F8" t="n">
-        <v>19.44898639194725</v>
+        <v>3.160460288691429</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>5.149830329211577</v>
+        <v>0.8368474284968812</v>
       </c>
       <c r="D9" t="n">
-        <v>5.456165194335481</v>
+        <v>0.8866268440795158</v>
       </c>
       <c r="E9" t="n">
-        <v>19.14907586987314</v>
+        <v>3.111724828854385</v>
       </c>
       <c r="F9" t="n">
-        <v>19.44898639194725</v>
+        <v>3.160460288691429</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>45.95549945337447</v>
+        <v>7.467768661173352</v>
       </c>
       <c r="D10" t="n">
-        <v>46.22573434121407</v>
+        <v>7.511681830447287</v>
       </c>
       <c r="E10" t="n">
-        <v>19.14907586987314</v>
+        <v>3.111724828854385</v>
       </c>
       <c r="F10" t="n">
-        <v>19.44898639194725</v>
+        <v>3.160460288691429</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>48.4369048514271</v>
+        <v>7.870997038356904</v>
       </c>
       <c r="D11" t="n">
-        <v>48.87676783589198</v>
+        <v>7.942474773332446</v>
       </c>
       <c r="E11" t="n">
-        <v>19.14907586987314</v>
+        <v>3.111724828854385</v>
       </c>
       <c r="F11" t="n">
-        <v>19.44898639194725</v>
+        <v>3.160460288691429</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>42.36812443995538</v>
+        <v>6.88482022149275</v>
       </c>
       <c r="D12" t="n">
-        <v>42.89651562089322</v>
+        <v>6.970683788395148</v>
       </c>
       <c r="E12" t="n">
-        <v>19.14907586987314</v>
+        <v>3.111724828854385</v>
       </c>
       <c r="F12" t="n">
-        <v>19.44898639194725</v>
+        <v>3.160460288691429</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>40.48925112698655</v>
+        <v>6.579503308135315</v>
       </c>
       <c r="D13" t="n">
-        <v>41.28251429481149</v>
+        <v>6.708408572906867</v>
       </c>
       <c r="E13" t="n">
-        <v>19.14907586987314</v>
+        <v>3.111724828854385</v>
       </c>
       <c r="F13" t="n">
-        <v>19.44898639194725</v>
+        <v>3.160460288691429</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>57.05207143917116</v>
+        <v>9.270961608865314</v>
       </c>
       <c r="D14" t="n">
-        <v>57.9904820566253</v>
+        <v>9.423453334201611</v>
       </c>
       <c r="E14" t="n">
-        <v>19.14907586987314</v>
+        <v>3.111724828854385</v>
       </c>
       <c r="F14" t="n">
-        <v>19.44898639194725</v>
+        <v>3.160460288691429</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>66.41227908867097</v>
+        <v>10.79199535190903</v>
       </c>
       <c r="D15" t="n">
-        <v>67.24561568315497</v>
+        <v>10.92741254851268</v>
       </c>
       <c r="E15" t="n">
-        <v>19.14907586987314</v>
+        <v>3.111724828854385</v>
       </c>
       <c r="F15" t="n">
-        <v>19.44898639194725</v>
+        <v>3.160460288691429</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>64.90143451664807</v>
+        <v>10.54648310895531</v>
       </c>
       <c r="D16" t="n">
-        <v>65.82254843208331</v>
+        <v>10.69616412021354</v>
       </c>
       <c r="E16" t="n">
-        <v>19.14907586987314</v>
+        <v>3.111724828854385</v>
       </c>
       <c r="F16" t="n">
-        <v>19.44898639194725</v>
+        <v>3.160460288691429</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>68.42810989890199</v>
+        <v>11.11956785857157</v>
       </c>
       <c r="D17" t="n">
-        <v>69.32403347795311</v>
+        <v>11.26515544016738</v>
       </c>
       <c r="E17" t="n">
-        <v>19.14907586987314</v>
+        <v>3.111724828854385</v>
       </c>
       <c r="F17" t="n">
-        <v>19.44898639194725</v>
+        <v>3.160460288691429</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
